--- a/test-output/FitnessCenter.xlsx
+++ b/test-output/FitnessCenter.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t>#</t>
   </si>
@@ -56,25 +56,10 @@
     <t>3</t>
   </si>
   <si>
-    <t>Fitness Center Services</t>
-  </si>
-  <si>
-    <t>7D Health Plus Fitness Studios</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>Fitness Center</t>
-  </si>
-  <si>
-    <t>Flash Properietor Mathangi R</t>
-  </si>
-  <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>SSJ Medicare</t>
   </si>
 </sst>
 </file>
@@ -142,7 +127,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="1.9296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.3125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="16.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="30.34375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="6.1953125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="7.9296875" customWidth="true" bestFit="true"/>
@@ -204,50 +189,50 @@
         <v>13</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
